--- a/artfynd/A 23157-2019 artfynd.xlsx
+++ b/artfynd/A 23157-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23157-2019 artfynd.xlsx
+++ b/artfynd/A 23157-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6767,6 +6767,122 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>118121319</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97744</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>504</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gucku viksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>695984</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6637498</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>ca 200</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Olle Amcoff</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Olle Amcoff</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
